--- a/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,2</t>
+          <t>1,25; 5,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 12,43</t>
+          <t>5,12; 11,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,84</t>
+          <t>3,24; 8,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 13,32</t>
+          <t>6,59; 13,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,85</t>
+          <t>0,79; 4,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 17,71</t>
+          <t>9,11; 18,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,96</t>
+          <t>5,56; 12,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 13,37</t>
+          <t>7,99; 13,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,34</t>
+          <t>1,4; 4,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,13</t>
+          <t>7,99; 13,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,99</t>
+          <t>5,18; 9,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,7</t>
+          <t>7,9; 12,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 10,65</t>
+          <t>5,45; 10,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 11,09</t>
+          <t>5,89; 11,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,41</t>
+          <t>2,01; 5,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 21,33</t>
+          <t>13,33; 21,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,62</t>
+          <t>5,45; 10,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,94</t>
+          <t>5,75; 10,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,08</t>
+          <t>2,48; 6,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,99</t>
+          <t>12,89; 18,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,61</t>
+          <t>6,12; 9,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,96</t>
+          <t>6,49; 9,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,07</t>
+          <t>2,58; 5,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,86; 18,57</t>
+          <t>13,93; 18,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,28</t>
+          <t>0,96; 4,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,78</t>
+          <t>4,74; 11,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,51</t>
+          <t>0,58; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 16,59</t>
+          <t>9,73; 16,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,32</t>
+          <t>1,28; 5,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,31</t>
+          <t>5,48; 11,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,95</t>
+          <t>1,85; 5,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,17</t>
+          <t>8,39; 13,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,05</t>
+          <t>1,42; 3,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,37</t>
+          <t>5,87; 10,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,05</t>
+          <t>1,55; 4,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,08</t>
+          <t>9,77; 14,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,17</t>
+          <t>1,08; 4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,01</t>
+          <t>3,66; 8,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,75</t>
+          <t>5,6; 11,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,59</t>
+          <t>3,96; 11,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,75</t>
+          <t>3,02; 7,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 12,88</t>
+          <t>6,94; 13,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 14,98</t>
+          <t>7,64; 14,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,16</t>
+          <t>2,16; 5,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,21</t>
+          <t>2,47; 5,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,88</t>
+          <t>5,91; 9,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,0</t>
+          <t>7,49; 12,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,31</t>
+          <t>3,23; 7,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,42</t>
+          <t>4,76; 12,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 18,94</t>
+          <t>8,71; 18,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,33</t>
+          <t>4,05; 11,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,94</t>
+          <t>4,62; 10,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,65</t>
+          <t>6,17; 15,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,14; 25,8</t>
+          <t>14,77; 25,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,91</t>
+          <t>4,13; 11,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,81</t>
+          <t>3,84; 9,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,19</t>
+          <t>6,59; 12,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,9; 19,97</t>
+          <t>13,21; 20,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,04</t>
+          <t>4,81; 9,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,11</t>
+          <t>4,9; 9,4</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,11</t>
+          <t>3,35; 9,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,16</t>
+          <t>5,2; 12,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 26,31</t>
+          <t>17,01; 25,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,2</t>
+          <t>1,12; 5,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,32</t>
+          <t>7,62; 15,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 13,57</t>
+          <t>6,0; 13,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,12; 23,9</t>
+          <t>16,05; 24,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,95</t>
+          <t>0,78; 3,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,28</t>
+          <t>6,59; 11,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,8</t>
+          <t>6,69; 11,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,87; 23,52</t>
+          <t>17,78; 23,42</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,62</t>
+          <t>4,02; 7,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,24</t>
+          <t>4,76; 9,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,23</t>
+          <t>2,69; 5,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,81</t>
+          <t>8,71; 13,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,95</t>
+          <t>4,01; 7,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,09</t>
+          <t>5,73; 10,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,1</t>
+          <t>4,38; 8,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 63,38</t>
+          <t>12,33; 66,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,19</t>
+          <t>4,45; 7,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,04</t>
+          <t>5,91; 9,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,54</t>
+          <t>3,93; 6,46</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 53,91</t>
+          <t>11,31; 50,66</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,76</t>
+          <t>5,0; 8,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,89</t>
+          <t>4,9; 8,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,12</t>
+          <t>5,25; 8,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,93</t>
+          <t>1,92; 7,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,81</t>
+          <t>7,48; 11,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,23</t>
+          <t>4,57; 8,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,59</t>
+          <t>5,64; 9,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,27</t>
+          <t>6,88; 10,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,64</t>
+          <t>6,62; 9,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,81</t>
+          <t>5,17; 7,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,86</t>
+          <t>6,02; 8,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,77</t>
+          <t>4,04; 7,89</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,83</t>
+          <t>4,3; 5,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,27</t>
+          <t>6,48; 8,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,36</t>
+          <t>4,78; 6,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,35; 11,76</t>
+          <t>8,11; 11,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,13</t>
+          <t>5,49; 7,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,09; 10,04</t>
+          <t>8,12; 10,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,77</t>
+          <t>6,07; 7,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,52; 31,24</t>
+          <t>10,51; 31,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,25</t>
+          <t>5,13; 6,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,89</t>
+          <t>7,56; 8,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,89</t>
+          <t>5,61; 6,87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,32; 22,62</t>
+          <t>10,27; 21,01</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3578; 16922</t>
+          <t>3400; 15886</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15640; 36638</t>
+          <t>15084; 33500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9353; 25956</t>
+          <t>9510; 26241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20088; 41495</t>
+          <t>20536; 42738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2100; 12648</t>
+          <t>2060; 12536</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26233; 50863</t>
+          <t>26167; 51985</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16854; 37409</t>
+          <t>16042; 37185</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23323; 38738</t>
+          <t>23150; 39202</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7545; 23167</t>
+          <t>7474; 23574</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46369; 76402</t>
+          <t>46510; 76856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30740; 58184</t>
+          <t>30178; 56388</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48461; 76328</t>
+          <t>47477; 74605</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26819; 52521</t>
+          <t>26853; 52965</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29429; 56083</t>
+          <t>29797; 56355</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10196; 27205</t>
+          <t>10086; 26353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69916; 110585</t>
+          <t>69082; 112625</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27453; 53520</t>
+          <t>27471; 50889</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31411; 57285</t>
+          <t>30092; 56474</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13099; 31792</t>
+          <t>12983; 31992</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66170; 92657</t>
+          <t>66383; 92905</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60578; 95813</t>
+          <t>61052; 95916</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65902; 102485</t>
+          <t>66820; 102490</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27769; 52039</t>
+          <t>26450; 52873</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>143239; 191931</t>
+          <t>143919; 192048</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2956; 13637</t>
+          <t>3058; 14662</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15431; 38185</t>
+          <t>15346; 35644</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1815; 11171</t>
+          <t>1849; 10602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29368; 52446</t>
+          <t>30742; 52772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4408; 17859</t>
+          <t>4285; 16776</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18277; 38578</t>
+          <t>18682; 40573</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6248; 20018</t>
+          <t>6208; 19346</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29963; 49465</t>
+          <t>29278; 48267</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10153; 26499</t>
+          <t>9272; 25841</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39201; 68985</t>
+          <t>39022; 67873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9478; 26512</t>
+          <t>10146; 26566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64182; 93653</t>
+          <t>65019; 95668</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3633; 14967</t>
+          <t>3861; 14734</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13996; 33689</t>
+          <t>13671; 33012</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20840; 43473</t>
+          <t>20707; 43209</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12503; 36233</t>
+          <t>12366; 35940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11582; 28793</t>
+          <t>11227; 28158</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26237; 50110</t>
+          <t>26989; 51004</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29607; 57998</t>
+          <t>29605; 56689</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9767; 29306</t>
+          <t>10287; 28208</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17581; 38070</t>
+          <t>18046; 38672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45047; 75363</t>
+          <t>45120; 74686</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57810; 90877</t>
+          <t>56708; 94842</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26502; 57600</t>
+          <t>25466; 57281</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10156; 25255</t>
+          <t>9671; 25398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18888; 40280</t>
+          <t>18530; 39744</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8874; 23925</t>
+          <t>8564; 23659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8610; 19558</t>
+          <t>8255; 19375</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12874; 30421</t>
+          <t>12803; 31144</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33237; 56656</t>
+          <t>32434; 55439</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9279; 23852</t>
+          <t>9028; 24732</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9969; 25383</t>
+          <t>9927; 25760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27594; 50099</t>
+          <t>27083; 50277</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55739; 86310</t>
+          <t>57095; 89218</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21214; 43163</t>
+          <t>20686; 42444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21117; 39870</t>
+          <t>21459; 41118</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6862</t>
+          <t>0; 6782</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8336; 24946</t>
+          <t>9188; 25462</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14630; 31984</t>
+          <t>13679; 32167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46211; 70928</t>
+          <t>45864; 69267</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3133; 14453</t>
+          <t>3103; 15314</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21448; 42890</t>
+          <t>21332; 43441</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16084; 37067</t>
+          <t>16389; 36366</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41434; 61431</t>
+          <t>41262; 61752</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4212; 16213</t>
+          <t>4268; 16559</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36117; 62468</t>
+          <t>36486; 63000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35810; 63264</t>
+          <t>35855; 63520</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>94138; 123895</t>
+          <t>93630; 123340</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24839; 46881</t>
+          <t>24747; 48426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32638; 61237</t>
+          <t>31531; 61540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18115; 40920</t>
+          <t>17632; 38902</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54029; 86194</t>
+          <t>54389; 85475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25829; 50748</t>
+          <t>25619; 50048</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40490; 70030</t>
+          <t>39785; 71331</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29906; 56013</t>
+          <t>30304; 57012</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>104052; 538269</t>
+          <t>104734; 567236</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>56333; 90120</t>
+          <t>55766; 88459</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80491; 122694</t>
+          <t>80114; 122768</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53577; 88169</t>
+          <t>52955; 87106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>170580; 794377</t>
+          <t>166700; 746560</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36065; 65154</t>
+          <t>37190; 65343</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38787; 69261</t>
+          <t>38214; 66476</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40279; 71019</t>
+          <t>40906; 69974</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18527; 64356</t>
+          <t>17856; 64982</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>57966; 92513</t>
+          <t>58610; 90984</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38339; 67836</t>
+          <t>37658; 68143</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47155; 79259</t>
+          <t>46632; 79840</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>49245; 73693</t>
+          <t>49398; 72076</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>102901; 147305</t>
+          <t>101108; 146917</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>83803; 125235</t>
+          <t>82940; 124259</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>97341; 142213</t>
+          <t>96610; 140599</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>63338; 127991</t>
+          <t>66486; 129953</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>139518; 191126</t>
+          <t>140911; 188514</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>219117; 283385</t>
+          <t>222019; 282813</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>161060; 215899</t>
+          <t>162097; 216780</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>288845; 406715</t>
+          <t>280643; 412039</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>183046; 240842</t>
+          <t>185394; 242778</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>287725; 357100</t>
+          <t>289062; 360613</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>214419; 275554</t>
+          <t>215180; 277386</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>390677; 1159719</t>
+          <t>390238; 1157341</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>338131; 415727</t>
+          <t>341330; 414212</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>527507; 620899</t>
+          <t>527858; 621491</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>392163; 478357</t>
+          <t>389233; 476535</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>739944; 1622589</t>
+          <t>736831; 1507037</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,82</t>
+          <t>1,29; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,37</t>
+          <t>5,2; 11,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,93</t>
+          <t>3,49; 8,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,72</t>
+          <t>5,95; 12,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,81</t>
+          <t>0,82; 5,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 18,1</t>
+          <t>9,25; 17,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,88</t>
+          <t>5,58; 12,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,54</t>
+          <t>7,74; 12,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,42</t>
+          <t>1,51; 4,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,21</t>
+          <t>7,98; 13,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,68</t>
+          <t>5,18; 9,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,41</t>
+          <t>7,75; 11,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,74</t>
+          <t>5,69; 10,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 11,15</t>
+          <t>5,48; 10,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,24</t>
+          <t>2,06; 5,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 21,73</t>
+          <t>13,43; 21,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,1</t>
+          <t>5,63; 10,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,78</t>
+          <t>5,7; 10,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,12</t>
+          <t>2,6; 6,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,89; 18,04</t>
+          <t>12,74; 17,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,62</t>
+          <t>6,18; 9,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,96</t>
+          <t>6,53; 10,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,15</t>
+          <t>2,64; 5,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,93; 18,58</t>
+          <t>14,14; 18,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,6</t>
+          <t>0,9; 4,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,0</t>
+          <t>4,97; 11,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,33</t>
+          <t>0,71; 3,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 16,7</t>
+          <t>9,52; 16,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,0</t>
+          <t>1,3; 5,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,9</t>
+          <t>5,47; 11,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,75</t>
+          <t>1,85; 6,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,83</t>
+          <t>8,51; 13,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,95</t>
+          <t>1,45; 4,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,21</t>
+          <t>5,64; 10,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,06</t>
+          <t>1,53; 3,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,38</t>
+          <t>9,41; 13,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,11</t>
+          <t>1,05; 4,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,83</t>
+          <t>3,97; 9,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 11,68</t>
+          <t>5,88; 11,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,5</t>
+          <t>4,02; 11,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,58</t>
+          <t>3,1; 7,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 13,11</t>
+          <t>6,65; 12,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 14,64</t>
+          <t>7,94; 14,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,93</t>
+          <t>3,17; 7,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,3</t>
+          <t>2,56; 5,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,79</t>
+          <t>5,94; 9,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,52</t>
+          <t>7,5; 12,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,27</t>
+          <t>4,25; 8,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 12,49</t>
+          <t>5,0; 12,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 18,69</t>
+          <t>8,63; 18,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,2</t>
+          <t>4,19; 11,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,84</t>
+          <t>4,4; 10,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,0</t>
+          <t>6,08; 14,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 25,25</t>
+          <t>14,94; 26,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,31</t>
+          <t>4,15; 10,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,95</t>
+          <t>6,48; 11,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 12,23</t>
+          <t>6,66; 12,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,21; 20,64</t>
+          <t>13,0; 20,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,88</t>
+          <t>4,83; 9,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,4</t>
+          <t>6,28; 10,03</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,29</t>
+          <t>3,42; 9,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 12,23</t>
+          <t>5,37; 12,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,01; 25,69</t>
+          <t>16,72; 25,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,51</t>
+          <t>1,11; 5,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 15,51</t>
+          <t>8,1; 15,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 13,32</t>
+          <t>5,84; 13,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 24,02</t>
+          <t>15,69; 23,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,02</t>
+          <t>0,88; 3,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 11,37</t>
+          <t>6,41; 11,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,85</t>
+          <t>6,46; 11,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,78; 23,42</t>
+          <t>17,37; 23,25</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,87</t>
+          <t>4,04; 7,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,29</t>
+          <t>4,79; 9,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,93</t>
+          <t>2,88; 6,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 13,69</t>
+          <t>9,17; 14,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,84</t>
+          <t>4,05; 7,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,28</t>
+          <t>5,55; 10,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,25</t>
+          <t>4,3; 8,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,33; 66,79</t>
+          <t>12,12; 16,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,06</t>
+          <t>4,42; 6,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,05</t>
+          <t>5,86; 8,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,46</t>
+          <t>3,91; 6,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,31; 50,66</t>
+          <t>11,25; 14,57</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,79</t>
+          <t>4,96; 8,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,53</t>
+          <t>4,88; 8,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,99</t>
+          <t>5,23; 9,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,0</t>
+          <t>4,68; 8,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,61</t>
+          <t>7,33; 11,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,27</t>
+          <t>4,52; 8,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,66</t>
+          <t>5,73; 9,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,04</t>
+          <t>7,17; 10,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,62</t>
+          <t>6,79; 9,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,75</t>
+          <t>5,2; 7,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,76</t>
+          <t>6,0; 8,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,89</t>
+          <t>6,26; 8,75</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,75</t>
+          <t>4,23; 5,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,25</t>
+          <t>6,37; 8,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,39</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,91</t>
+          <t>9,81; 11,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,18</t>
+          <t>5,4; 7,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,12; 10,13</t>
+          <t>8,08; 10,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,83</t>
+          <t>6,01; 7,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,51; 31,18</t>
+          <t>10,65; 12,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,22</t>
+          <t>5,08; 6,19</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,9</t>
+          <t>7,56; 8,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 6,87</t>
+          <t>5,65; 6,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,01</t>
+          <t>10,52; 11,87</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29740</t>
+          <t>28164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>60008</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3400; 15886</t>
+          <t>3523; 15543</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15084; 33500</t>
+          <t>15328; 33225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9510; 26241</t>
+          <t>10239; 26225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20536; 42738</t>
+          <t>18956; 39228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2060; 12536</t>
+          <t>2132; 13160</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26167; 51985</t>
+          <t>26578; 51303</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16042; 37185</t>
+          <t>16106; 35676</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23150; 39202</t>
+          <t>24468; 40435</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7474; 23574</t>
+          <t>8084; 23790</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46510; 76856</t>
+          <t>46455; 77601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30178; 56388</t>
+          <t>30188; 57782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47477; 74605</t>
+          <t>49183; 74423</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>90504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>83225</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>167865</t>
+          <t>173729</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26853; 52965</t>
+          <t>28078; 53643</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29797; 56355</t>
+          <t>27710; 55280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10086; 26353</t>
+          <t>10342; 26560</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69082; 112625</t>
+          <t>71280; 112656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27471; 50889</t>
+          <t>28361; 51643</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30092; 56474</t>
+          <t>29830; 56600</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12983; 31992</t>
+          <t>13625; 33263</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66383; 92905</t>
+          <t>69601; 97714</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61052; 95916</t>
+          <t>61600; 95175</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66820; 102490</t>
+          <t>67258; 104901</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26450; 52873</t>
+          <t>27048; 53080</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>143919; 192048</t>
+          <t>152296; 199905</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78413</t>
+          <t>77307</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3058; 14662</t>
+          <t>2885; 13908</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15346; 35644</t>
+          <t>16113; 37494</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1849; 10602</t>
+          <t>2248; 10739</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30742; 52772</t>
+          <t>30082; 50560</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4285; 16776</t>
+          <t>4377; 16888</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18682; 40573</t>
+          <t>18651; 38461</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6208; 19346</t>
+          <t>6235; 20504</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29278; 48267</t>
+          <t>30341; 49468</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9272; 25841</t>
+          <t>9492; 26253</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39022; 67873</t>
+          <t>37510; 67267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10146; 26566</t>
+          <t>10045; 25472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65019; 95668</t>
+          <t>63243; 91158</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>45543</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3861; 14734</t>
+          <t>3758; 15260</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13671; 33012</t>
+          <t>14857; 34878</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20707; 43209</t>
+          <t>21764; 42774</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12366; 35940</t>
+          <t>15001; 41162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11227; 28158</t>
+          <t>11526; 28154</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26989; 51004</t>
+          <t>25853; 49438</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29605; 56689</t>
+          <t>30751; 56781</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10287; 28208</t>
+          <t>13360; 31842</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18046; 38672</t>
+          <t>18666; 38064</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45120; 74686</t>
+          <t>45333; 75829</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56708; 94842</t>
+          <t>56773; 92791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25466; 57281</t>
+          <t>33755; 67224</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>33940</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9671; 25398</t>
+          <t>10164; 25634</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18530; 39744</t>
+          <t>18342; 39435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8564; 23659</t>
+          <t>8858; 24355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8255; 19375</t>
+          <t>9044; 20575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12803; 31144</t>
+          <t>12623; 29947</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32434; 55439</t>
+          <t>32815; 57341</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9028; 24732</t>
+          <t>9078; 23716</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9927; 25760</t>
+          <t>14828; 25568</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27083; 50277</t>
+          <t>27360; 50789</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57095; 89218</t>
+          <t>56175; 87976</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20686; 42444</t>
+          <t>20770; 41634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21459; 41118</t>
+          <t>27297; 43582</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57024</t>
+          <t>56508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>51104</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>107612</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6782</t>
+          <t>0; 6771</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9188; 25462</t>
+          <t>9366; 25926</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13679; 32167</t>
+          <t>14129; 32370</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45864; 69267</t>
+          <t>45251; 67817</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3103; 15314</t>
+          <t>3093; 14693</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21332; 43441</t>
+          <t>22689; 44620</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16389; 36366</t>
+          <t>15946; 37079</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41262; 61752</t>
+          <t>41393; 60934</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4268; 16559</t>
+          <t>4833; 16762</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36486; 63000</t>
+          <t>35537; 62374</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35855; 63520</t>
+          <t>34664; 62219</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93630; 123340</t>
+          <t>92857; 124244</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>288552</t>
+          <t>109955</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>357572</t>
+          <t>191531</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24747; 48426</t>
+          <t>24819; 48290</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31531; 61540</t>
+          <t>31779; 60408</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17632; 38902</t>
+          <t>18937; 40846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54389; 85475</t>
+          <t>66013; 102749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25619; 50048</t>
+          <t>25817; 49213</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39785; 71331</t>
+          <t>38512; 69698</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30304; 57012</t>
+          <t>29722; 56452</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>104734; 567236</t>
+          <t>93604; 128612</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>55766; 88459</t>
+          <t>55383; 87543</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>80114; 122768</t>
+          <t>79514; 118563</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52955; 87106</t>
+          <t>52651; 87475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>166700; 746560</t>
+          <t>167835; 217294</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43150</t>
+          <t>48815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>60441</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>103591</t>
+          <t>121421</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>37190; 65343</t>
+          <t>36877; 64029</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38214; 66476</t>
+          <t>38014; 67904</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40906; 69974</t>
+          <t>40740; 72456</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17856; 64982</t>
+          <t>37326; 64818</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>58610; 90984</t>
+          <t>57454; 92491</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37658; 68143</t>
+          <t>37207; 67027</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46632; 79840</t>
+          <t>47378; 80242</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>49398; 72076</t>
+          <t>59585; 87933</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>101108; 146917</t>
+          <t>103760; 146074</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>82940; 124259</t>
+          <t>83321; 124097</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96610; 140599</t>
+          <t>96223; 139963</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>66486; 129953</t>
+          <t>101961; 142630</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>946100</t>
+          <t>811091</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>140911; 188514</t>
+          <t>138475; 189999</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>222019; 282813</t>
+          <t>218116; 285421</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>162097; 216780</t>
+          <t>163918; 217219</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>280643; 412039</t>
+          <t>346484; 422103</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>185394; 242778</t>
+          <t>182438; 241226</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>289062; 360613</t>
+          <t>287533; 360504</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>215180; 277386</t>
+          <t>213063; 274503</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>390238; 1157341</t>
+          <t>398113; 463994</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>341330; 414212</t>
+          <t>338008; 411953</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>527858; 621491</t>
+          <t>527790; 627280</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>389233; 476535</t>
+          <t>392156; 470234</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>736831; 1507037</t>
+          <t>764914; 862677</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
